--- a/rosstat/data/work_in_speciality_spo.xlsx
+++ b/rosstat/data/work_in_speciality_spo.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlenaK\Documents\4semester\TRPP\employmentSite\employmentsite\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlenaK\Documents\6semester\sipi\project_sipi\rosstat\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{027B21AD-0C0D-4DBE-9D74-D27A431F4EB9}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{232D46C5-991C-47EA-8E58-ACEF2A986F85}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2712" yWindow="2256" windowWidth="17280" windowHeight="8964" xr2:uid="{FFFED6D9-FA79-4CB9-BD6A-C1A1A6A47FE8}"/>
+    <workbookView xWindow="2268" yWindow="2268" windowWidth="17280" windowHeight="9732" xr2:uid="{FFFED6D9-FA79-4CB9-BD6A-C1A1A6A47FE8}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
